--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/may-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M50"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>58000000.24</v>
+        <v>64614.03</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>35332290</v>
+        <v>39361.41</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>15408611.47</v>
+        <v>17165.73</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>50465844.87</v>
+        <v>56220.72</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>31670100.7</v>
+        <v>35281.6</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>21150800.58</v>
+        <v>23562.73</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>18899100.43</v>
+        <v>21054.26</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>65667883.05</v>
+        <v>73156.32000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>58615354</v>
+        <v>65299.55</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>42251611.64</v>
+        <v>47069.77</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>35863744</v>
+        <v>39953.46</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>27192690</v>
+        <v>30293.61</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11615699.48</v>
+        <v>12940.3</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>23015790</v>
+        <v>25640.39</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13150600.75</v>
+        <v>14650.23</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>24705799.44</v>
+        <v>27523.12</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>35323013.95</v>
+        <v>39351.07</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26646480</v>
+        <v>29685.11</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>34833204</v>
+        <v>38805.41</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>66763348.26</v>
+        <v>74376.7</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>29750699.72</v>
+        <v>33143.32</v>
       </c>
     </row>
     <row r="23">
@@ -1846,11 +1846,11 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>30591000.37</v>
+        <v>34079.44</v>
       </c>
     </row>
     <row r="24">
@@ -1907,11 +1907,11 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>37160999.89</v>
+        <v>41398.65</v>
       </c>
     </row>
     <row r="25">
@@ -1968,11 +1968,11 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>63340199.02</v>
+        <v>70563.2</v>
       </c>
     </row>
     <row r="26">
@@ -2029,17 +2029,17 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>50390999.82</v>
+        <v>56137.34</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3824-64-CM26</t>
+          <t>5155-106-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.261.400-3</t>
+          <t>60.504.000-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
+          <t>Servicio Electoral</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,28 +2079,28 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>37463580</v>
+        <v>25640.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5155-106-CM26</t>
+          <t>3824-64-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.504.000-4</t>
+          <t>69.261.400-3</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>I MUNICIPALIDAD DE PADRE HURTADO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,22 +2140,22 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>23015790</v>
+        <v>41735.74</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>70543200</v>
+        <v>78587.59</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>51413446</v>
+        <v>57276.38</v>
       </c>
     </row>
     <row r="31">
@@ -2334,11 +2334,11 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>33200001.59</v>
+        <v>36985.96</v>
       </c>
     </row>
     <row r="32">
@@ -2395,11 +2395,11 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>30390500.84</v>
+        <v>33856.08</v>
       </c>
     </row>
     <row r="33">
@@ -2456,17 +2456,17 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>24250514.96</v>
+        <v>27015.92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2436-578-CM26</t>
+          <t>3807-213-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.120.200-3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2506,28 +2506,28 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12421932.81</v>
+        <v>38823.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3807-213-CM26</t>
+          <t>3799-175-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,37 +2552,37 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>69.180.200-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>I MUNICIPALIDAD DE PUREN</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>34849230.92</v>
+        <v>14650.23</v>
       </c>
     </row>
     <row r="36">
@@ -2639,17 +2639,17 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>35332290</v>
+        <v>39361.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3799-175-CM26</t>
+          <t>2436-600-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,43 +2674,43 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.180.200-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUREN</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>91.139.000-0</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>13150600.75</v>
+        <v>13838.47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3938-173-CM26</t>
+          <t>4993-261-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2730,17 +2730,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.252.400-4</t>
+          <t>69.265.000-k</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
+          <t>MUNICIPALIDAD DE CHOLCHOL</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2761,17 +2761,17 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>34821000.55</v>
+        <v>39581.29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2436-600-CM26</t>
+          <t>3889-247-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,43 +2796,43 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.090.200-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE PLACILLA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AUTOMOTORA COMERCIAL COSTABAL Y ECHENIQUE S A</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>91.139.000-0</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>12421932.81</v>
+        <v>14338.52</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4993-261-CM26</t>
+          <t>4690-165-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2857,43 +2857,43 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.265.000-k</t>
+          <t>69.110.900-3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE CHOLCHOL</t>
+          <t>I MUNICIPALIDAD DE MAULE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>35529666.97</v>
+        <v>13548.53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3889-247-CM26</t>
+          <t>3594-334-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2913,48 +2913,48 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.090.200-1</t>
+          <t>69.140.200-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PLACILLA</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>12870800.81</v>
+        <v>35934.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4690-165-CM26</t>
+          <t>3594-332-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2974,22 +2974,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.110.900-3</t>
+          <t>69.140.200-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULE</t>
+          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3005,17 +3005,17 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>12161675.05</v>
+        <v>17885.04</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3594-334-CM26</t>
+          <t>3938-173-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,43 +3040,43 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.140.200-2</t>
+          <t>69.252.400-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CURARREHUE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>32256198.31</v>
+        <v>38791.81</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3594-332-CM26</t>
+          <t>3637-146-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3101,43 +3101,43 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.140.200-2</t>
+          <t>69.251.500-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PORTEZUELO</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16054290</v>
+        <v>56081.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3637-146-CM26</t>
+          <t>2337-48-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,47 +3152,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.251.500-5</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>50340499.79</v>
+        <v>54587.71</v>
       </c>
     </row>
     <row r="46">
@@ -3249,11 +3249,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>34821000.55</v>
+        <v>38791.81</v>
       </c>
     </row>
     <row r="47">
@@ -3310,11 +3310,11 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>22802315.9</v>
+        <v>25402.58</v>
       </c>
     </row>
     <row r="48">
@@ -3371,17 +3371,17 @@
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>37734067</v>
+        <v>42037.07</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2337-48-CM26</t>
+          <t>2924-31-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,103 +3401,42 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>48999999.3</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2924-31-CM26</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>may-2026</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-05-29</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>69.030.100-8</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Atacama</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>SUMMIT MOTORS S.A.</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>37160999.89</v>
+        <v>41398.65</v>
       </c>
     </row>
   </sheetData>
